--- a/artfynd/A 54800-2023 artfynd.xlsx
+++ b/artfynd/A 54800-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54800-2023 artfynd.xlsx
+++ b/artfynd/A 54800-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,6 +787,121 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>114987454</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97555</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>A 54800, Greby, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>574481</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6406778</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54800-2023 artfynd.xlsx
+++ b/artfynd/A 54800-2023 artfynd.xlsx
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119569124</v>
+        <v>119569066</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>57326</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,35 +917,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -953,13 +953,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574482</v>
+        <v>574481</v>
       </c>
       <c r="R4" t="n">
-        <v>6406779</v>
+        <v>6406778</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,7 +997,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1016,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119569066</v>
+        <v>119569124</v>
       </c>
       <c r="B5" t="n">
-        <v>57326</v>
+        <v>97907</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,35 +1027,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1064,13 +1063,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574481</v>
+        <v>574482</v>
       </c>
       <c r="R5" t="n">
-        <v>6406778</v>
+        <v>6406779</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,6 +1107,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
